--- a/Datos/Diccionario_base_municipal  - Copy (1).xlsx
+++ b/Datos/Diccionario_base_municipal  - Copy (1).xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniandes-my.sharepoint.com/personal/mc_caraballo_uniandes_edu_co/Documents/Universidad/MECA/Evaluación/Trabajo final/Datos/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniandes-my.sharepoint.com/personal/mc_caraballo_uniandes_edu_co/Documents/Universidad/MECA/Big Data y Machine Learning/Repositorios/BD_ML_taller_1/Trabajo-Final--Evaluaci-n-de-impacto/Datos/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="85" documentId="13_ncr:1_{8F806FFB-7806-4535-AEA5-F0CDE6E8C01B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D0BECD0-0BD4-426C-B16B-CF95D3787AE4}"/>
   <bookViews>
-    <workbookView xWindow="2300" yWindow="10690" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{F08A5A44-9A0F-4E3B-8392-D8DA4584EB0A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{F08A5A44-9A0F-4E3B-8392-D8DA4584EB0A}"/>
   </bookViews>
   <sheets>
     <sheet name="Dicionario Variables" sheetId="1" r:id="rId1"/>
@@ -281,7 +281,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -289,11 +289,10 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -305,7 +304,7 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -836,94 +835,93 @@
   <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="39" style="6" customWidth="1"/>
-    <col min="2" max="2" width="55.85546875" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="71.7109375" style="6" customWidth="1"/>
-    <col min="4" max="4" width="55" style="6" customWidth="1"/>
-    <col min="5" max="16384" width="9.140625" style="5"/>
+    <col min="1" max="1" width="39" style="5" customWidth="1"/>
+    <col min="2" max="2" width="55.85546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="71.7109375" style="5" customWidth="1"/>
+    <col min="4" max="4" width="55" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="8" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="114" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="6" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="5" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="90" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="6" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="120" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="5" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="75" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="10" t="s">
         <v>56</v>
       </c>
     </row>
